--- a/C_codespace/2 kurs/3-rd senester/Algorithms and Data Structure/Laboratory work/Laba #2/Vlad/Книга1.xlsx
+++ b/C_codespace/2 kurs/3-rd senester/Algorithms and Data Structure/Laboratory work/Laba #2/Vlad/Книга1.xlsx
@@ -5,16 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Codespace\C_codespace\2 kurs\3-rd senester\Algorithms and data structure\2-nd lab\Vlad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Codespace\C_codespace\2 kurs\3-rd senester\Algorithms and data structure\Laboratory work\Laba #2\Vlad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5626FC5-A7E8-43EA-937A-3DE61A0FF6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDFCF48-9A60-4604-890C-DC37DD1B8B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="330" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -124,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -140,13 +139,6 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -155,6 +147,12 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1031,64 +1029,64 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>133</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>165</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>165</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>214</c:v>
+                  <c:v>92</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>197</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>276</c:v>
+                  <c:v>83</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>243</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>332</c:v>
+                  <c:v>94</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>259</c:v>
+                  <c:v>87</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>228</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>227</c:v>
+                  <c:v>77</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>374</c:v>
+                  <c:v>87</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>431</c:v>
+                  <c:v>83</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>306</c:v>
+                  <c:v>86</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>260</c:v>
+                  <c:v>86</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>296</c:v>
+                  <c:v>122</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>316</c:v>
+                  <c:v>106</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>340</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>338</c:v>
+                  <c:v>107</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>520</c:v>
+                  <c:v>89</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1145,64 +1143,64 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>22</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>69</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>96</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>127</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>139</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>464</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>468</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>468</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>466</c:v>
-                </c:pt>
                 <c:pt idx="9">
-                  <c:v>475</c:v>
+                  <c:v>57</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>478</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>482</c:v>
+                  <c:v>73</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>488</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>494</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>498</c:v>
+                  <c:v>79</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>505</c:v>
+                  <c:v>77</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>509</c:v>
+                  <c:v>77</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>510</c:v>
+                  <c:v>83</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>532</c:v>
+                  <c:v>103</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>560</c:v>
+                  <c:v>79</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1259,64 +1257,64 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>114</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>182</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>183</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>285</c:v>
+                  <c:v>113</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>240</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>262</c:v>
+                  <c:v>73</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>223</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>297</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>273</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>396</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>278</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>258</c:v>
+                  <c:v>74</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>255</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>288</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>267</c:v>
+                  <c:v>76</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>278</c:v>
+                  <c:v>79</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>284</c:v>
+                  <c:v>74</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>380</c:v>
+                  <c:v>113</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>296</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>320</c:v>
+                  <c:v>77</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2801,14 +2799,14 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>520777</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>41049</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>148167</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>508000</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>74083</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>169333</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3101,48 +3099,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="38.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="9"/>
     <col min="6" max="6" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="38.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27.42578125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="9"/>
-    <col min="11" max="11" width="13.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="9.140625" style="9"/>
+    <col min="11" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="7" t="s">
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="K1" s="10">
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="K1" s="7">
         <v>1000</v>
       </c>
-      <c r="L1" s="9">
-        <v>114</v>
+      <c r="L1">
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="7"/>
+      <c r="A2" s="10"/>
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
@@ -3152,8 +3147,8 @@
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="7"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="10"/>
       <c r="G2" s="3" t="s">
         <v>1</v>
       </c>
@@ -3163,11 +3158,11 @@
       <c r="I2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="7">
         <v>2000</v>
       </c>
-      <c r="L2" s="9">
-        <v>182</v>
+      <c r="L2">
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -3183,24 +3178,24 @@
       <c r="D3" s="5">
         <v>260</v>
       </c>
-      <c r="E3" s="11"/>
+      <c r="E3" s="8"/>
       <c r="F3" s="1">
         <v>1000</v>
       </c>
       <c r="G3" s="6">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="H3" s="6">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I3" s="6">
-        <v>114</v>
-      </c>
-      <c r="K3" s="10">
+        <v>33</v>
+      </c>
+      <c r="K3" s="7">
         <v>3000</v>
       </c>
-      <c r="L3" s="9">
-        <v>183</v>
+      <c r="L3">
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -3216,24 +3211,24 @@
       <c r="D4" s="5">
         <v>344</v>
       </c>
-      <c r="E4" s="11"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="1">
         <v>2000</v>
       </c>
       <c r="G4" s="6">
-        <v>165</v>
+        <v>72</v>
       </c>
       <c r="H4" s="6">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="I4" s="6">
-        <v>182</v>
-      </c>
-      <c r="K4" s="10">
+        <v>70</v>
+      </c>
+      <c r="K4" s="7">
         <v>4000</v>
       </c>
-      <c r="L4" s="9">
-        <v>285</v>
+      <c r="L4">
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -3249,24 +3244,24 @@
       <c r="D5" s="5">
         <v>489</v>
       </c>
-      <c r="E5" s="11"/>
+      <c r="E5" s="8"/>
       <c r="F5" s="1">
         <v>3000</v>
       </c>
       <c r="G5" s="6">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="H5" s="6">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="I5" s="6">
-        <v>183</v>
-      </c>
-      <c r="K5" s="10">
+        <v>56</v>
+      </c>
+      <c r="K5" s="7">
         <v>5000</v>
       </c>
-      <c r="L5" s="9">
-        <v>240</v>
+      <c r="L5">
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -3282,24 +3277,24 @@
       <c r="D6" s="5">
         <v>537</v>
       </c>
-      <c r="E6" s="11"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="1">
         <v>4000</v>
       </c>
       <c r="G6" s="6">
-        <v>214</v>
+        <v>92</v>
       </c>
       <c r="H6" s="6">
-        <v>127</v>
+        <v>40</v>
       </c>
       <c r="I6" s="6">
-        <v>285</v>
-      </c>
-      <c r="K6" s="10">
+        <v>113</v>
+      </c>
+      <c r="K6" s="7">
         <v>6000</v>
       </c>
-      <c r="L6" s="9">
-        <v>262</v>
+      <c r="L6">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -3315,24 +3310,24 @@
       <c r="D7" s="5">
         <v>698</v>
       </c>
-      <c r="E7" s="11"/>
+      <c r="E7" s="8"/>
       <c r="F7" s="1">
         <v>5000</v>
       </c>
       <c r="G7" s="6">
-        <v>197</v>
+        <v>71</v>
       </c>
       <c r="H7" s="6">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="I7" s="6">
-        <v>240</v>
-      </c>
-      <c r="K7" s="10">
+        <v>71</v>
+      </c>
+      <c r="K7" s="7">
         <v>7000</v>
       </c>
-      <c r="L7" s="9">
-        <v>223</v>
+      <c r="L7">
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -3348,24 +3343,24 @@
       <c r="D8" s="5">
         <v>716</v>
       </c>
-      <c r="E8" s="11"/>
+      <c r="E8" s="8"/>
       <c r="F8" s="1">
         <v>6000</v>
       </c>
       <c r="G8" s="6">
-        <v>276</v>
+        <v>83</v>
       </c>
       <c r="H8" s="6">
-        <v>464</v>
+        <v>82</v>
       </c>
       <c r="I8" s="6">
-        <v>262</v>
-      </c>
-      <c r="K8" s="10">
+        <v>73</v>
+      </c>
+      <c r="K8" s="7">
         <v>8000</v>
       </c>
-      <c r="L8" s="9">
-        <v>297</v>
+      <c r="L8">
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -3381,24 +3376,24 @@
       <c r="D9" s="5">
         <v>449</v>
       </c>
-      <c r="E9" s="11"/>
+      <c r="E9" s="8"/>
       <c r="F9" s="1">
         <v>7000</v>
       </c>
       <c r="G9" s="6">
-        <v>243</v>
+        <v>66</v>
       </c>
       <c r="H9" s="6">
-        <v>468</v>
+        <v>58</v>
       </c>
       <c r="I9" s="6">
-        <v>223</v>
-      </c>
-      <c r="K9" s="10">
+        <v>66</v>
+      </c>
+      <c r="K9" s="7">
         <v>9000</v>
       </c>
-      <c r="L9" s="9">
-        <v>273</v>
+      <c r="L9">
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -3414,24 +3409,24 @@
       <c r="D10" s="5">
         <v>491</v>
       </c>
-      <c r="E10" s="11"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="1">
         <v>8000</v>
       </c>
       <c r="G10" s="6">
-        <v>332</v>
+        <v>94</v>
       </c>
       <c r="H10" s="6">
-        <v>468</v>
+        <v>57</v>
       </c>
       <c r="I10" s="6">
-        <v>297</v>
-      </c>
-      <c r="K10" s="10">
+        <v>70</v>
+      </c>
+      <c r="K10" s="7">
         <v>10000</v>
       </c>
-      <c r="L10" s="9">
-        <v>396</v>
+      <c r="L10">
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -3447,24 +3442,24 @@
       <c r="D11" s="5">
         <v>480</v>
       </c>
-      <c r="E11" s="11"/>
+      <c r="E11" s="8"/>
       <c r="F11" s="1">
         <v>9000</v>
       </c>
       <c r="G11" s="6">
-        <v>259</v>
+        <v>87</v>
       </c>
       <c r="H11" s="6">
-        <v>466</v>
+        <v>69</v>
       </c>
       <c r="I11" s="6">
-        <v>273</v>
-      </c>
-      <c r="K11" s="10">
+        <v>80</v>
+      </c>
+      <c r="K11" s="7">
         <v>11000</v>
       </c>
-      <c r="L11" s="9">
-        <v>278</v>
+      <c r="L11">
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -3480,24 +3475,24 @@
       <c r="D12" s="5">
         <v>658</v>
       </c>
-      <c r="E12" s="11"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="1">
         <v>10000</v>
       </c>
       <c r="G12" s="6">
-        <v>228</v>
+        <v>69</v>
       </c>
       <c r="H12" s="6">
-        <v>475</v>
+        <v>57</v>
       </c>
       <c r="I12" s="6">
-        <v>396</v>
-      </c>
-      <c r="K12" s="10">
+        <v>67</v>
+      </c>
+      <c r="K12" s="7">
         <v>12000</v>
       </c>
-      <c r="L12" s="9">
-        <v>258</v>
+      <c r="L12">
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -3513,24 +3508,24 @@
       <c r="D13" s="5">
         <v>584</v>
       </c>
-      <c r="E13" s="11"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="1">
         <v>11000</v>
       </c>
       <c r="G13" s="6">
-        <v>227</v>
+        <v>77</v>
       </c>
       <c r="H13" s="6">
-        <v>478</v>
+        <v>72</v>
       </c>
       <c r="I13" s="6">
-        <v>278</v>
-      </c>
-      <c r="K13" s="10">
+        <v>70</v>
+      </c>
+      <c r="K13" s="7">
         <v>13000</v>
       </c>
-      <c r="L13" s="9">
-        <v>255</v>
+      <c r="L13">
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -3546,24 +3541,24 @@
       <c r="D14" s="5">
         <v>490</v>
       </c>
-      <c r="E14" s="11"/>
+      <c r="E14" s="8"/>
       <c r="F14" s="1">
         <v>12000</v>
       </c>
       <c r="G14" s="6">
-        <v>374</v>
+        <v>87</v>
       </c>
       <c r="H14" s="6">
-        <v>482</v>
+        <v>73</v>
       </c>
       <c r="I14" s="6">
-        <v>258</v>
-      </c>
-      <c r="K14" s="10">
+        <v>74</v>
+      </c>
+      <c r="K14" s="7">
         <v>14000</v>
       </c>
-      <c r="L14" s="9">
-        <v>288</v>
+      <c r="L14">
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -3579,24 +3574,24 @@
       <c r="D15" s="5">
         <v>488</v>
       </c>
-      <c r="E15" s="11"/>
+      <c r="E15" s="8"/>
       <c r="F15" s="1">
         <v>13000</v>
       </c>
       <c r="G15" s="6">
-        <v>431</v>
+        <v>83</v>
       </c>
       <c r="H15" s="6">
-        <v>488</v>
+        <v>72</v>
       </c>
       <c r="I15" s="6">
-        <v>255</v>
-      </c>
-      <c r="K15" s="10">
+        <v>72</v>
+      </c>
+      <c r="K15" s="7">
         <v>15000</v>
       </c>
-      <c r="L15" s="9">
-        <v>267</v>
+      <c r="L15">
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -3612,24 +3607,24 @@
       <c r="D16" s="5">
         <v>511</v>
       </c>
-      <c r="E16" s="11"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="1">
         <v>14000</v>
       </c>
       <c r="G16" s="6">
-        <v>306</v>
+        <v>86</v>
       </c>
       <c r="H16" s="6">
-        <v>494</v>
+        <v>75</v>
       </c>
       <c r="I16" s="6">
-        <v>288</v>
-      </c>
-      <c r="K16" s="10">
+        <v>70</v>
+      </c>
+      <c r="K16" s="7">
         <v>16000</v>
       </c>
-      <c r="L16" s="9">
-        <v>278</v>
+      <c r="L16">
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -3645,24 +3640,24 @@
       <c r="D17" s="5">
         <v>547</v>
       </c>
-      <c r="E17" s="11"/>
+      <c r="E17" s="8"/>
       <c r="F17" s="1">
         <v>15000</v>
       </c>
       <c r="G17" s="6">
-        <v>260</v>
+        <v>86</v>
       </c>
       <c r="H17" s="6">
-        <v>498</v>
+        <v>79</v>
       </c>
       <c r="I17" s="6">
-        <v>267</v>
-      </c>
-      <c r="K17" s="10">
+        <v>76</v>
+      </c>
+      <c r="K17" s="7">
         <v>17000</v>
       </c>
-      <c r="L17" s="9">
-        <v>284</v>
+      <c r="L17">
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -3678,24 +3673,24 @@
       <c r="D18" s="5">
         <v>635</v>
       </c>
-      <c r="E18" s="11"/>
+      <c r="E18" s="8"/>
       <c r="F18" s="1">
         <v>16000</v>
       </c>
       <c r="G18" s="6">
-        <v>296</v>
+        <v>122</v>
       </c>
       <c r="H18" s="6">
-        <v>505</v>
+        <v>77</v>
       </c>
       <c r="I18" s="6">
-        <v>278</v>
-      </c>
-      <c r="K18" s="10">
+        <v>79</v>
+      </c>
+      <c r="K18" s="7">
         <v>18000</v>
       </c>
-      <c r="L18" s="9">
-        <v>380</v>
+      <c r="L18">
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -3711,24 +3706,24 @@
       <c r="D19" s="5">
         <v>614</v>
       </c>
-      <c r="E19" s="11"/>
+      <c r="E19" s="8"/>
       <c r="F19" s="1">
         <v>17000</v>
       </c>
       <c r="G19" s="6">
-        <v>316</v>
+        <v>106</v>
       </c>
       <c r="H19" s="6">
-        <v>509</v>
+        <v>77</v>
       </c>
       <c r="I19" s="6">
-        <v>284</v>
-      </c>
-      <c r="K19" s="10">
+        <v>74</v>
+      </c>
+      <c r="K19" s="7">
         <v>19000</v>
       </c>
-      <c r="L19" s="9">
-        <v>296</v>
+      <c r="L19">
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -3744,24 +3739,24 @@
       <c r="D20" s="5">
         <v>638</v>
       </c>
-      <c r="E20" s="11"/>
+      <c r="E20" s="8"/>
       <c r="F20" s="1">
         <v>18000</v>
       </c>
       <c r="G20" s="6">
-        <v>340</v>
+        <v>80</v>
       </c>
       <c r="H20" s="6">
-        <v>510</v>
+        <v>83</v>
       </c>
       <c r="I20" s="6">
-        <v>380</v>
-      </c>
-      <c r="K20" s="10">
+        <v>113</v>
+      </c>
+      <c r="K20" s="7">
         <v>20000</v>
       </c>
-      <c r="L20" s="9">
-        <v>320</v>
+      <c r="L20">
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -3777,20 +3772,20 @@
       <c r="D21" s="5">
         <v>629</v>
       </c>
-      <c r="E21" s="11"/>
+      <c r="E21" s="8"/>
       <c r="F21" s="1">
         <v>19000</v>
       </c>
       <c r="G21" s="6">
-        <v>338</v>
+        <v>107</v>
       </c>
       <c r="H21" s="6">
-        <v>532</v>
+        <v>103</v>
       </c>
       <c r="I21" s="6">
-        <v>296</v>
-      </c>
-      <c r="K21" s="11"/>
+        <v>75</v>
+      </c>
+      <c r="K21" s="8"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -3805,32 +3800,32 @@
       <c r="D22" s="5">
         <v>657</v>
       </c>
-      <c r="E22" s="11"/>
+      <c r="E22" s="8"/>
       <c r="F22" s="1">
         <v>20000</v>
       </c>
       <c r="G22" s="6">
-        <v>520</v>
+        <v>89</v>
       </c>
       <c r="H22" s="6">
-        <v>560</v>
+        <v>79</v>
       </c>
       <c r="I22" s="6">
-        <v>320</v>
-      </c>
-      <c r="K22" s="11"/>
+        <v>77</v>
+      </c>
+      <c r="K22" s="8"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
-      <c r="E23" s="11"/>
+      <c r="E23" s="8"/>
       <c r="F23" s="1"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
-      <c r="K23" s="11"/>
+      <c r="K23" s="8"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
@@ -3846,96 +3841,99 @@
         <f t="shared" si="0"/>
         <v>545.75</v>
       </c>
-      <c r="E24" s="11"/>
+      <c r="E24" s="8"/>
       <c r="F24" s="1"/>
       <c r="G24" s="5">
         <f>AVERAGE(G3:G22)</f>
-        <v>281</v>
+        <v>84.65</v>
       </c>
       <c r="H24" s="5">
         <f t="shared" ref="H24:I24" si="1">AVERAGE(H3:H22)</f>
-        <v>392.5</v>
+        <v>64.2</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="1"/>
-        <v>267.95</v>
-      </c>
-      <c r="K24" s="11"/>
+        <v>73.95</v>
+      </c>
+      <c r="K24" s="8"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
-      <c r="E25" s="11">
+      <c r="E25" s="8">
         <f>1/E26</f>
-        <v>1.9389209285072742</v>
+        <v>7.9590466005962659</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
-      <c r="K25" s="11"/>
+      <c r="K25" s="8"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="5">
         <f>G24/B24</f>
-        <v>0.4986690328305235</v>
+        <v>0.15022182786157942</v>
       </c>
       <c r="C26" s="5">
         <f t="shared" ref="C26:D26" si="2">H24/C24</f>
-        <v>0.55760761471799969</v>
+        <v>9.1206137235402759E-2</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="2"/>
-        <v>0.49097572148419605</v>
-      </c>
-      <c r="E26" s="12">
+        <v>0.13550160329821348</v>
+      </c>
+      <c r="E26" s="9">
         <f>AVERAGE(B26:D26)</f>
-        <v>0.51575078967757315</v>
+        <v>0.12564318946506522</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
-      <c r="K26" s="11"/>
+      <c r="K26" s="8"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
-      <c r="E27" s="11"/>
+      <c r="E27" s="8"/>
       <c r="F27" s="1"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
-      <c r="K27" s="11"/>
+      <c r="K27" s="8"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
-      <c r="E28" s="11"/>
+      <c r="E28" s="8"/>
       <c r="F28" s="1"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
-      <c r="K28" s="11"/>
+      <c r="K28" s="8"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="11"/>
+      <c r="E29" s="8"/>
       <c r="F29" s="1"/>
-      <c r="G29" s="6"/>
+      <c r="G29" s="6">
+        <f>H24/I24</f>
+        <v>0.86815415821501019</v>
+      </c>
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
-      <c r="K29" s="11"/>
+      <c r="K29" s="8"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
@@ -3946,29 +3944,32 @@
       <c r="C30" s="5"/>
       <c r="D30" s="5">
         <f>AVERAGE(G30,B30)</f>
-        <v>0.72899917927687685</v>
-      </c>
-      <c r="E30" s="11"/>
+        <v>0.96359617909829476</v>
+      </c>
+      <c r="E30" s="8"/>
       <c r="F30" s="1"/>
       <c r="G30" s="5">
         <f>I24/H24</f>
-        <v>0.68267515923566879</v>
+        <v>1.1518691588785046</v>
       </c>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
-      <c r="K30" s="11"/>
+      <c r="K30" s="8"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="11"/>
+      <c r="E31" s="8"/>
       <c r="F31" s="1"/>
-      <c r="G31" s="6"/>
+      <c r="G31" s="6">
+        <f>H24/G24</f>
+        <v>0.75841701122268157</v>
+      </c>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
-      <c r="K31" s="11"/>
+      <c r="K31" s="8"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
@@ -3978,15 +3979,15 @@
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
-      <c r="E32" s="11"/>
+      <c r="E32" s="8"/>
       <c r="F32" s="1"/>
       <c r="G32" s="5">
         <f>I24/G24</f>
-        <v>0.95355871886120991</v>
+        <v>0.87359716479621974</v>
       </c>
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
-      <c r="K32" s="11"/>
+      <c r="K32" s="8"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
@@ -3994,230 +3995,230 @@
       <c r="C33" s="5"/>
       <c r="D33" s="5">
         <f>AVERAGE(G32,B32)</f>
-        <v>0.9610295812584666</v>
-      </c>
-      <c r="E33" s="11"/>
+        <v>0.92104880422597146</v>
+      </c>
+      <c r="E33" s="8"/>
       <c r="F33" s="1"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
-      <c r="K33" s="11"/>
+      <c r="K33" s="8"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
-      <c r="E34" s="11"/>
+      <c r="E34" s="8"/>
       <c r="F34" s="1"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
-      <c r="K34" s="11"/>
+      <c r="K34" s="8"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
-      <c r="E35" s="11"/>
+      <c r="E35" s="8"/>
       <c r="F35" s="1"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
-      <c r="K35" s="11"/>
+      <c r="K35" s="8"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
-      <c r="E36" s="11"/>
+      <c r="E36" s="8"/>
       <c r="F36" s="1"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
-      <c r="K36" s="11"/>
+      <c r="K36" s="8"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
-      <c r="E37" s="11"/>
+      <c r="E37" s="8"/>
       <c r="F37" s="1"/>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
-      <c r="K37" s="11"/>
+      <c r="K37" s="8"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
-      <c r="E38" s="11"/>
+      <c r="E38" s="8"/>
       <c r="F38" s="1"/>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
-      <c r="K38" s="11"/>
+      <c r="K38" s="8"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
-      <c r="E39" s="11"/>
+      <c r="E39" s="8"/>
       <c r="F39" s="1"/>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
-      <c r="K39" s="11"/>
+      <c r="K39" s="8"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
-      <c r="E40" s="11"/>
+      <c r="E40" s="8"/>
       <c r="F40" s="1"/>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
-      <c r="K40" s="11"/>
+      <c r="K40" s="8"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
-      <c r="E41" s="11"/>
+      <c r="E41" s="8"/>
       <c r="F41" s="1"/>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
-      <c r="K41" s="11"/>
+      <c r="K41" s="8"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
-      <c r="E42" s="11"/>
+      <c r="E42" s="8"/>
       <c r="F42" s="1"/>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
-      <c r="K42" s="11"/>
+      <c r="K42" s="8"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
-      <c r="E43" s="11"/>
+      <c r="E43" s="8"/>
       <c r="F43" s="1"/>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
-      <c r="K43" s="11"/>
+      <c r="K43" s="8"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
-      <c r="E44" s="11"/>
+      <c r="E44" s="8"/>
       <c r="F44" s="1"/>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
-      <c r="K44" s="11"/>
+      <c r="K44" s="8"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
-      <c r="E45" s="11"/>
+      <c r="E45" s="8"/>
       <c r="F45" s="1"/>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
-      <c r="K45" s="11"/>
+      <c r="K45" s="8"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
-      <c r="E46" s="11"/>
+      <c r="E46" s="8"/>
       <c r="F46" s="1"/>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
-      <c r="K46" s="11"/>
+      <c r="K46" s="8"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
-      <c r="E47" s="11"/>
+      <c r="E47" s="8"/>
       <c r="F47" s="1"/>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
       <c r="I47" s="6"/>
-      <c r="K47" s="11"/>
+      <c r="K47" s="8"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
-      <c r="E48" s="11"/>
+      <c r="E48" s="8"/>
       <c r="F48" s="1"/>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
       <c r="I48" s="6"/>
-      <c r="K48" s="11"/>
+      <c r="K48" s="8"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
-      <c r="E49" s="11"/>
+      <c r="E49" s="8"/>
       <c r="F49" s="1"/>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
       <c r="I49" s="6"/>
-      <c r="K49" s="11"/>
+      <c r="K49" s="8"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
-      <c r="E50" s="11"/>
+      <c r="E50" s="8"/>
       <c r="F50" s="1"/>
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
       <c r="I50" s="6"/>
-      <c r="K50" s="11"/>
+      <c r="K50" s="8"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
-      <c r="E51" s="11"/>
+      <c r="E51" s="8"/>
       <c r="F51" s="1"/>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
       <c r="I51" s="6"/>
-      <c r="K51" s="11"/>
+      <c r="K51" s="8"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
@@ -4239,13 +4240,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80AA11AF-8229-45EF-BB3E-6BBFA1A0C147}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>